--- a/translations/15.7.0/global_diff.xlsx
+++ b/translations/15.7.0/global_diff.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="翻译差异" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翻译差异" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'翻译差异'!$A$1:$I$546</definedName>
@@ -16215,19 +16215,19 @@
       <c r="C462" s="2" t="inlineStr"/>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr"/>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr"/>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I462" s="2" t="inlineStr"/>
@@ -16246,19 +16246,19 @@
       <c r="C463" s="2" t="inlineStr"/>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr"/>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I463" s="2" t="inlineStr"/>
@@ -16401,19 +16401,19 @@
       <c r="C468" s="2" t="inlineStr"/>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr"/>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr"/>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr"/>
@@ -16432,19 +16432,19 @@
       <c r="C469" s="2" t="inlineStr"/>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr"/>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr"/>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I469" s="2" t="inlineStr"/>
@@ -16525,19 +16525,19 @@
       <c r="C472" s="2" t="inlineStr"/>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I472" s="2" t="inlineStr"/>
@@ -16556,19 +16556,19 @@
       <c r="C473" s="2" t="inlineStr"/>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr"/>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr"/>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I473" s="2" t="inlineStr"/>
@@ -16587,19 +16587,19 @@
       <c r="C474" s="2" t="inlineStr"/>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr"/>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr"/>
       <c r="H474" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I474" s="2" t="inlineStr"/>
@@ -16618,19 +16618,19 @@
       <c r="C475" s="2" t="inlineStr"/>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr"/>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr"/>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I475" s="2" t="inlineStr"/>
@@ -16711,19 +16711,19 @@
       <c r="C478" s="2" t="inlineStr"/>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr"/>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr"/>
@@ -16742,19 +16742,19 @@
       <c r="C479" s="2" t="inlineStr"/>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr"/>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I479" s="2" t="inlineStr"/>

--- a/translations/15.7.0/global_diff.xlsx
+++ b/translations/15.7.0/global_diff.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="翻译差异" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="翻译差异" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'翻译差异'!$A$1:$I$546</definedName>
@@ -16215,19 +16215,19 @@
       <c r="C462" s="2" t="inlineStr"/>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr"/>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G462" s="2" t="inlineStr"/>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I462" s="2" t="inlineStr"/>
@@ -16246,19 +16246,19 @@
       <c r="C463" s="2" t="inlineStr"/>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr"/>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I463" s="2" t="inlineStr"/>
@@ -16401,19 +16401,19 @@
       <c r="C468" s="2" t="inlineStr"/>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr"/>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G468" s="2" t="inlineStr"/>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr"/>
@@ -16432,19 +16432,19 @@
       <c r="C469" s="2" t="inlineStr"/>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr"/>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G469" s="2" t="inlineStr"/>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I469" s="2" t="inlineStr"/>
@@ -16525,19 +16525,19 @@
       <c r="C472" s="2" t="inlineStr"/>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr"/>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I472" s="2" t="inlineStr"/>
@@ -16556,19 +16556,19 @@
       <c r="C473" s="2" t="inlineStr"/>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr"/>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr"/>
       <c r="H473" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I473" s="2" t="inlineStr"/>
@@ -16587,19 +16587,19 @@
       <c r="C474" s="2" t="inlineStr"/>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr"/>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr"/>
       <c r="H474" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I474" s="2" t="inlineStr"/>
@@ -16618,19 +16618,19 @@
       <c r="C475" s="2" t="inlineStr"/>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr"/>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr"/>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I475" s="2" t="inlineStr"/>
@@ -16711,19 +16711,19 @@
       <c r="C478" s="2" t="inlineStr"/>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr"/>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr"/>
@@ -16742,19 +16742,19 @@
       <c r="C479" s="2" t="inlineStr"/>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr"/>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I479" s="2" t="inlineStr"/>
